--- a/ExcelData/NBData.xlsx
+++ b/ExcelData/NBData.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kayesha\Desktop\sprint\NoBrokerProject\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEA4BAAB-FC33-49CE-B145-5A28902C8291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B316AED-0BA0-4F5A-B80A-F8C5CA5D3A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2620" yWindow="2620" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2620" yWindow="2620" windowWidth="14400" windowHeight="7270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,19 +26,22 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>BaseUrl</t>
   </si>
   <si>
     <t>https://www.nobroker.in</t>
   </si>
+  <si>
+    <t>Chennai</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -52,6 +56,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -75,9 +85,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -381,4 +393,29 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CE271AB-25E0-40EB-BE2F-13571B6B6E32}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="25.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2"/>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>